--- a/doc/新标日初级上册形容词表.xlsx
+++ b/doc/新标日初级上册形容词表.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="形容词表" sheetId="1" r:id="R244eaf5b494c4f1b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="R836a68735aa8437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="形容词表" sheetId="1" r:id="R385db419ec684618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明与统计" sheetId="2" r:id="R72ffb0f35adb406b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1442,23 +1442,6 @@
     <x:t xml:space="preserve">跨课复现 / 补充</x:t>
   </x:si>
   <x:si>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Microsoft YaHei"/>
-      </x:rPr>
-      <x:t xml:space="preserve">25 </x:t>
-    </x:r>
-    <x:r>
-      <x:rPr>
-        <x:sz val="11"/>
-        <x:rFont val="Source Han Sans SC"/>
-        <x:family val="2"/>
-      </x:rPr>
-      <x:t xml:space="preserve">条（橙色底纹），含比较句、简体形、复习课中的复现，以及应用课文补充词。</x:t>
-    </x:r>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">音调说明</x:t>
   </x:si>
   <x:si>
@@ -1520,9 +1503,6 @@
   </x:si>
   <x:si>
     <x:t xml:space="preserve">首次收录数</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">合计</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1533,7 +1513,7 @@
     <x:numFmt numFmtId="164" formatCode="General"/>
     <x:numFmt numFmtId="165" formatCode="General"/>
   </x:numFmts>
-  <x:fonts count="13">
+  <x:fonts count="17">
     <x:font>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
@@ -1594,8 +1574,29 @@
       <x:color rgb="FF000000"/>
       <x:name val="Microsoft YaHei"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Source Han Sans SC"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="Calibri"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="6">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -1605,6 +1606,16 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF2F5597"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFDF2E9"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -1665,7 +1676,7 @@
     <x:xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <x:xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="1" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="51">
     <x:xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="0" applyBorder="0" applyAlignment="0">
       <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
     </x:xf>
@@ -1751,6 +1762,72 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="164" fontId="11" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="12" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="bottom" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="general" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="12" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="164" fontId="11" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="left" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -4910,6 +4987,64 @@
         <x:v>用户补充；第19课</x:v>
       </x:c>
     </x:row>
+    <x:row r="99">
+      <x:c r="A99" s="35" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B99" s="36" t="str">
+        <x:v>悲しい</x:v>
+      </x:c>
+      <x:c r="C99" s="36" t="str">
+        <x:v>かなしい</x:v>
+      </x:c>
+      <x:c r="D99" s="36" t="str">
+        <x:v>一类形容词（形1）</x:v>
+      </x:c>
+      <x:c r="E99" s="37" t="str">
+        <x:v>悲伤、悲哀</x:v>
+      </x:c>
+      <x:c r="F99" s="36" t="str">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="G99" s="36" t="str">
+        <x:v>かなしく</x:v>
+      </x:c>
+      <x:c r="H99" s="36" t="str">
+        <x:v>かなしかった</x:v>
+      </x:c>
+      <x:c r="I99" s="37" t="str">
+        <x:v>用户补充；初级下册第36课</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100">
+      <x:c r="A100" s="48" t="n">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B100" s="49" t="str">
+        <x:v>おかしい</x:v>
+      </x:c>
+      <x:c r="C100" s="49" t="str">
+        <x:v>おかしい</x:v>
+      </x:c>
+      <x:c r="D100" s="49" t="str">
+        <x:v>一类形容词（形1）</x:v>
+      </x:c>
+      <x:c r="E100" s="50" t="str">
+        <x:v>奇怪、不正常</x:v>
+      </x:c>
+      <x:c r="F100" s="49" t="str">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="G100" s="49" t="str">
+        <x:v>おかしく</x:v>
+      </x:c>
+      <x:c r="H100" s="49" t="str">
+        <x:v>おかしかった</x:v>
+      </x:c>
+      <x:c r="I100" s="50" t="str">
+        <x:v>用户补充；第24课</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -4954,7 +5089,7 @@
         <x:v>474</x:v>
       </x:c>
       <x:c r="B5" s="14" t="n">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="15" hidden="0" customHeight="1">
@@ -4962,76 +5097,76 @@
         <x:v>475</x:v>
       </x:c>
       <x:c r="B6" s="14" t="str">
-        <x:v>72 条（一类形容词 47 条、二类形容词 25 条）</x:v>
+        <x:v>73 条（一类形容词 48 条、二类形容词 25 条）</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="15" hidden="0" customHeight="1">
       <x:c r="A7" s="15" t="s">
         <x:v>476</x:v>
       </x:c>
-      <x:c r="B7" s="14" t="s">
-        <x:v>477</x:v>
+      <x:c r="B7" s="14" t="str">
+        <x:v>26 条（橙色底纹），含比较句、简体形、复习课中的复现、应用课文补充词及用户补充词。</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="15" hidden="0" customHeight="1">
       <x:c r="A8" s="15" t="s">
-        <x:v>478</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="B8" s="16" t="str">
-        <x:v>除「遅い」标为“0”外，其余词条均标为“⚠待核”。未取得可逐项复核的书内注音，网络辞书音调与教材随书音频可能不同；核书时请对照课末词汇表、书末总词汇表与音频。</x:v>
+        <x:v>「遅い」「悲しい」标为“0”，“おかしい”标为“3”，其余词条均标为“⚠待核”。未取得可逐项复核的书内注音，网络辞书音调与教材随书音频可能不同；核书时请对照课末词汇表、书末总词汇表与音频。</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="15" hidden="0" customHeight="1">
       <x:c r="A9" s="15" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="B9" s="16" t="s">
         <x:v>479</x:v>
-      </x:c>
-      <x:c r="B9" s="16" t="s">
-        <x:v>480</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="15" hidden="0" customHeight="1">
       <x:c r="A10" s="15" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B10" s="16" t="s">
         <x:v>481</x:v>
-      </x:c>
-      <x:c r="B10" s="16" t="s">
-        <x:v>482</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="15" hidden="0" customHeight="1">
       <x:c r="A11" s="15" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="B11" s="16" t="s">
         <x:v>483</x:v>
-      </x:c>
-      <x:c r="B11" s="16" t="s">
-        <x:v>484</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="15" hidden="0" customHeight="1">
       <x:c r="A12" s="15" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B12" s="16" t="s">
         <x:v>485</x:v>
-      </x:c>
-      <x:c r="B12" s="16" t="s">
-        <x:v>486</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="15" hidden="0" customHeight="1">
       <x:c r="A13" s="15" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B13" s="16" t="s">
         <x:v>487</x:v>
-      </x:c>
-      <x:c r="B13" s="16" t="s">
-        <x:v>488</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="15" hidden="0" customHeight="1">
       <x:c r="A14" s="15" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B14" s="16" t="s">
         <x:v>489</x:v>
-      </x:c>
-      <x:c r="B14" s="16" t="s">
-        <x:v>490</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="15" hidden="0" customHeight="1">
       <x:c r="A15" s="15" t="s">
-        <x:v>491</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B15" s="16" t="str">
         <x:v>熱い＝物体/液体温度高；暑い＝天气气温高。早い＝时间早；速い＝速度快；遅い＝晚、慢。</x:v>
@@ -5039,26 +5174,26 @@
     </x:row>
     <x:row r="16" ht="15" hidden="0" customHeight="1">
       <x:c r="A16" s="15" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B16" s="16" t="s">
         <x:v>492</x:v>
-      </x:c>
-      <x:c r="B16" s="16" t="s">
-        <x:v>493</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="15" hidden="0" customHeight="1">
       <x:c r="A17" s="15" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="B17" s="16" t="s">
         <x:v>494</x:v>
-      </x:c>
-      <x:c r="B17" s="16" t="s">
-        <x:v>495</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="15" hidden="0" customHeight="1">
       <x:c r="A18" s="15" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="B18" s="16" t="s">
         <x:v>496</x:v>
-      </x:c>
-      <x:c r="B18" s="16" t="s">
-        <x:v>497</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="15" hidden="0" customHeight="1">
@@ -5066,7 +5201,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="B20" s="17" t="s">
-        <x:v>498</x:v>
+        <x:v>497</x:v>
       </x:c>
       <x:c r="C20" s="17" t="s">
         <x:v>474</x:v>
@@ -5231,23 +5366,34 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B35" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="n">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="15" hidden="0" customHeight="1">
+      <x:c r="A36" s="41" t="n">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="B36" s="41" t="n">
+        <x:f aca="0"/>
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" ht="15" hidden="0" customHeight="1">
-      <x:c r="A36" s="18" t="s">
-        <x:v>499</x:v>
-      </x:c>
-      <x:c r="B36" s="19" t="n">
+      <x:c r="C36" s="41" t="n">
         <x:f aca="0"/>
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="C36" s="19" t="n">
-        <x:f aca="0"/>
-        <x:v>97</x:v>
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37">
+      <x:c r="A37" s="39" t="str">
+        <x:v>合计</x:v>
+      </x:c>
+      <x:c r="B37" s="40" t="n">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="C37" s="40" t="n">
+        <x:v>99</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
